--- a/artfynd/A 4330-2026 artfynd.xlsx
+++ b/artfynd/A 4330-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131458777</v>
       </c>
       <c r="B2" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4330-2026 artfynd.xlsx
+++ b/artfynd/A 4330-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131458777</v>
       </c>
       <c r="B2" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4330-2026 artfynd.xlsx
+++ b/artfynd/A 4330-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131458777</v>
       </c>
       <c r="B2" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4330-2026 artfynd.xlsx
+++ b/artfynd/A 4330-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131458777</v>
+        <v>125306472</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
+        <v>99781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>222309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyängen SSO om , Srm</t>
+          <t>Jägarstugan N om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590663</v>
+        <v>590574</v>
       </c>
       <c r="R2" t="n">
-        <v>6542485</v>
+        <v>6542417</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131458777</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyängen SSO om , Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590663</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6542485</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4330-2026 artfynd.xlsx
+++ b/artfynd/A 4330-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125306472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131458777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>